--- a/分省数据看板（月度）/趋势分析/25年4月.xlsx
+++ b/分省数据看板（月度）/趋势分析/25年4月.xlsx
@@ -29,12 +29,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>名称</t>
   </si>
   <si>
     <t>活跃用户</t>
+  </si>
+  <si>
+    <t>新用户</t>
   </si>
   <si>
     <t>营收</t>
@@ -531,27 +534,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="9">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -678,7 +666,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
@@ -690,34 +678,34 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="0">
@@ -806,25 +794,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="3">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="3" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1138,13 +1126,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <dimension ref="A1:G35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
-    <col min="5" max="5" width="12.625"/>
+    <col min="6" max="6" width="12.625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1160,754 +1148,859 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="4">
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="5">
         <v>6506</v>
       </c>
       <c r="C2" s="5">
+        <v>3243</v>
+      </c>
+      <c r="D2" s="5">
         <v>30159</v>
       </c>
-      <c r="D2" s="5">
+      <c r="E2" s="5">
         <v>4626</v>
       </c>
-      <c r="E2" s="6">
-        <f t="shared" ref="E2:E35" si="0">C2/B2</f>
+      <c r="F2" s="6">
+        <f t="shared" ref="F2:F35" si="0">D2/B2</f>
         <v>4.63556716876729</v>
       </c>
-      <c r="F2" s="7">
-        <f>D2/B2</f>
+      <c r="G2" s="7">
+        <f>E2/B2</f>
         <v>0.711035966799877</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:7">
+      <c r="A3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="5">
+        <v>7740</v>
+      </c>
+      <c r="C3" s="5">
+        <v>3740</v>
+      </c>
+      <c r="D3" s="5">
+        <v>26718</v>
+      </c>
+      <c r="E3" s="5">
+        <v>5805</v>
+      </c>
+      <c r="F3" s="6">
+        <f t="shared" si="0"/>
+        <v>3.45193798449612</v>
+      </c>
+      <c r="G3" s="7">
+        <f t="shared" ref="G2:G35" si="1">E3/B3</f>
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="5">
+        <v>8437</v>
+      </c>
+      <c r="C4" s="5">
+        <v>4905</v>
+      </c>
+      <c r="D4" s="5">
+        <v>14818</v>
+      </c>
+      <c r="E4" s="5">
+        <v>5466</v>
+      </c>
+      <c r="F4" s="6">
+        <f t="shared" si="0"/>
+        <v>1.75631148512504</v>
+      </c>
+      <c r="G4" s="7">
+        <f t="shared" si="1"/>
+        <v>0.647860613962309</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="5">
+        <v>3709</v>
+      </c>
+      <c r="C5" s="5">
+        <v>2189</v>
+      </c>
+      <c r="D5" s="5">
+        <v>6562</v>
+      </c>
+      <c r="E5" s="5">
+        <v>2402</v>
+      </c>
+      <c r="F5" s="6">
+        <f t="shared" si="0"/>
+        <v>1.76921002965759</v>
+      </c>
+      <c r="G5" s="7">
+        <f t="shared" si="1"/>
+        <v>0.647613912105689</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="5">
+        <v>2946</v>
+      </c>
+      <c r="C6" s="5">
+        <v>1729</v>
+      </c>
+      <c r="D6" s="5">
+        <v>8930</v>
+      </c>
+      <c r="E6" s="5">
+        <v>1803</v>
+      </c>
+      <c r="F6" s="6">
+        <f t="shared" si="0"/>
+        <v>3.03122878479294</v>
+      </c>
+      <c r="G6" s="7">
+        <f t="shared" si="1"/>
+        <v>0.612016293279022</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="5">
+        <v>10854</v>
+      </c>
+      <c r="C7" s="5">
+        <v>4161</v>
+      </c>
+      <c r="D7" s="5">
+        <v>49571</v>
+      </c>
+      <c r="E7" s="5">
+        <v>7670</v>
+      </c>
+      <c r="F7" s="6">
+        <f t="shared" si="0"/>
+        <v>4.56707204717155</v>
+      </c>
+      <c r="G7" s="7">
+        <f t="shared" si="1"/>
+        <v>0.706651925557398</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="5">
+        <v>3695</v>
+      </c>
+      <c r="C8" s="5">
+        <v>1929</v>
+      </c>
+      <c r="D8" s="5">
+        <v>11077</v>
+      </c>
+      <c r="E8" s="5">
+        <v>2461</v>
+      </c>
+      <c r="F8" s="6">
+        <f t="shared" si="0"/>
+        <v>2.9978349120433</v>
+      </c>
+      <c r="G8" s="7">
+        <f t="shared" si="1"/>
+        <v>0.666035182679296</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="5">
+        <v>6530</v>
+      </c>
+      <c r="C9" s="5">
+        <v>2808</v>
+      </c>
+      <c r="D9" s="5">
+        <v>18479</v>
+      </c>
+      <c r="E9" s="5">
+        <v>4508</v>
+      </c>
+      <c r="F9" s="6">
+        <f t="shared" si="0"/>
+        <v>2.82986217457887</v>
+      </c>
+      <c r="G9" s="7">
+        <f t="shared" si="1"/>
+        <v>0.690352220520674</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="5">
+        <v>2843</v>
+      </c>
+      <c r="C10" s="5">
+        <v>1728</v>
+      </c>
+      <c r="D10" s="5">
+        <v>17024</v>
+      </c>
+      <c r="E10" s="5">
+        <v>1727</v>
+      </c>
+      <c r="F10" s="6">
+        <f t="shared" si="0"/>
+        <v>5.98804080196975</v>
+      </c>
+      <c r="G10" s="7">
+        <f t="shared" si="1"/>
+        <v>0.607456911712979</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="5">
+        <v>22242</v>
+      </c>
+      <c r="C11" s="5">
+        <v>11925</v>
+      </c>
+      <c r="D11" s="5">
+        <v>100389</v>
+      </c>
+      <c r="E11" s="5">
+        <v>15164</v>
+      </c>
+      <c r="F11" s="6">
+        <f t="shared" si="0"/>
+        <v>4.51348799568384</v>
+      </c>
+      <c r="G11" s="7">
+        <f t="shared" si="1"/>
+        <v>0.681773221832569</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="5">
+        <v>7876</v>
+      </c>
+      <c r="C12" s="5">
+        <v>4265</v>
+      </c>
+      <c r="D12" s="5">
+        <v>25577</v>
+      </c>
+      <c r="E12" s="5">
+        <v>5440</v>
+      </c>
+      <c r="F12" s="6">
+        <f t="shared" si="0"/>
+        <v>3.24746063991874</v>
+      </c>
+      <c r="G12" s="7">
+        <f t="shared" si="1"/>
+        <v>0.69070594210259</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="5">
+        <v>12645</v>
+      </c>
+      <c r="C13" s="5">
+        <v>5692</v>
+      </c>
+      <c r="D13" s="5">
+        <v>44180</v>
+      </c>
+      <c r="E13" s="5">
+        <v>8746</v>
+      </c>
+      <c r="F13" s="6">
+        <f t="shared" si="0"/>
+        <v>3.49387109529458</v>
+      </c>
+      <c r="G13" s="7">
+        <f t="shared" si="1"/>
+        <v>0.691656781336497</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="5">
+        <v>10297</v>
+      </c>
+      <c r="C14" s="5">
+        <v>4497</v>
+      </c>
+      <c r="D14" s="5">
+        <v>25981</v>
+      </c>
+      <c r="E14" s="5">
+        <v>7349</v>
+      </c>
+      <c r="F14" s="6">
+        <f t="shared" si="0"/>
+        <v>2.52316208604448</v>
+      </c>
+      <c r="G14" s="7">
+        <f t="shared" si="1"/>
+        <v>0.713703020297174</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="5">
+        <v>7671</v>
+      </c>
+      <c r="C15" s="5">
+        <v>4091</v>
+      </c>
+      <c r="D15" s="5">
+        <v>12346</v>
+      </c>
+      <c r="E15" s="5">
+        <v>5081</v>
+      </c>
+      <c r="F15" s="6">
+        <f t="shared" si="0"/>
+        <v>1.60943814365793</v>
+      </c>
+      <c r="G15" s="7">
+        <f t="shared" si="1"/>
+        <v>0.662364750358493</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" s="5">
+        <v>32810</v>
+      </c>
+      <c r="C16" s="5">
+        <v>14283</v>
+      </c>
+      <c r="D16" s="5">
+        <v>76191</v>
+      </c>
+      <c r="E16" s="5">
+        <v>24750</v>
+      </c>
+      <c r="F16" s="6">
+        <f t="shared" si="0"/>
+        <v>2.32218835720817</v>
+      </c>
+      <c r="G16" s="7">
+        <f t="shared" si="1"/>
+        <v>0.754343188052423</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" s="5">
+        <v>10347</v>
+      </c>
+      <c r="C17" s="5">
+        <v>5703</v>
+      </c>
+      <c r="D17" s="5">
+        <v>16527</v>
+      </c>
+      <c r="E17" s="5">
+        <v>6794</v>
+      </c>
+      <c r="F17" s="6">
+        <f t="shared" si="0"/>
+        <v>1.59727457233981</v>
+      </c>
+      <c r="G17" s="7">
+        <f t="shared" si="1"/>
+        <v>0.656615444090074</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" s="5">
+        <v>7978</v>
+      </c>
+      <c r="C18" s="5">
+        <v>3962</v>
+      </c>
+      <c r="D18" s="5">
+        <v>24456</v>
+      </c>
+      <c r="E18" s="5">
+        <v>5544</v>
+      </c>
+      <c r="F18" s="6">
+        <f t="shared" si="0"/>
+        <v>3.06542993231386</v>
+      </c>
+      <c r="G18" s="7">
+        <f t="shared" si="1"/>
+        <v>0.694911005264477</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="5">
+        <v>9037</v>
+      </c>
+      <c r="C19" s="5">
+        <v>4306</v>
+      </c>
+      <c r="D19" s="5">
+        <v>27480</v>
+      </c>
+      <c r="E19" s="5">
+        <v>6141</v>
+      </c>
+      <c r="F19" s="6">
+        <f t="shared" si="0"/>
+        <v>3.04083213455793</v>
+      </c>
+      <c r="G19" s="7">
+        <f t="shared" si="1"/>
+        <v>0.67953967024455</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" s="5">
+        <v>15700</v>
+      </c>
+      <c r="C20" s="5">
+        <v>7490</v>
+      </c>
+      <c r="D20" s="5">
+        <v>63799</v>
+      </c>
+      <c r="E20" s="5">
+        <v>10558</v>
+      </c>
+      <c r="F20" s="6">
+        <f t="shared" si="0"/>
+        <v>4.06363057324841</v>
+      </c>
+      <c r="G20" s="7">
+        <f t="shared" si="1"/>
+        <v>0.672484076433121</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" s="5">
+        <v>3127</v>
+      </c>
+      <c r="C21" s="5">
+        <v>1788</v>
+      </c>
+      <c r="D21" s="5">
+        <v>6319</v>
+      </c>
+      <c r="E21" s="5">
+        <v>2069</v>
+      </c>
+      <c r="F21" s="6">
+        <f t="shared" si="0"/>
+        <v>2.02078669651423</v>
+      </c>
+      <c r="G21" s="7">
+        <f t="shared" si="1"/>
+        <v>0.661656539814519</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22" s="5">
+        <v>1510</v>
+      </c>
+      <c r="C22" s="5">
+        <v>764</v>
+      </c>
+      <c r="D22" s="5">
+        <v>5033</v>
+      </c>
+      <c r="E22" s="5">
+        <v>1047</v>
+      </c>
+      <c r="F22" s="6">
+        <f t="shared" si="0"/>
+        <v>3.33311258278146</v>
+      </c>
+      <c r="G22" s="7">
+        <f t="shared" si="1"/>
+        <v>0.693377483443709</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" s="5">
+        <v>5003</v>
+      </c>
+      <c r="C23" s="5">
+        <v>2083</v>
+      </c>
+      <c r="D23" s="5">
+        <v>20436</v>
+      </c>
+      <c r="E23" s="5">
+        <v>3363</v>
+      </c>
+      <c r="F23" s="6">
+        <f t="shared" si="0"/>
+        <v>4.08474915050969</v>
+      </c>
+      <c r="G23" s="7">
+        <f t="shared" si="1"/>
+        <v>0.672196681990806</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B24" s="5">
+        <v>7095</v>
+      </c>
+      <c r="C24" s="5">
+        <v>3644</v>
+      </c>
+      <c r="D24" s="5">
+        <v>17938</v>
+      </c>
+      <c r="E24" s="5">
+        <v>4907</v>
+      </c>
+      <c r="F24" s="6">
+        <f t="shared" si="0"/>
+        <v>2.52825933756166</v>
+      </c>
+      <c r="G24" s="7">
+        <f t="shared" si="1"/>
+        <v>0.691613812544045</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B25" s="5">
+        <v>2320</v>
+      </c>
+      <c r="C25" s="5">
+        <v>1364</v>
+      </c>
+      <c r="D25" s="5">
+        <v>5343</v>
+      </c>
+      <c r="E25" s="5">
+        <v>1400</v>
+      </c>
+      <c r="F25" s="6">
+        <f t="shared" si="0"/>
+        <v>2.30301724137931</v>
+      </c>
+      <c r="G25" s="7">
+        <f t="shared" si="1"/>
+        <v>0.603448275862069</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B26" s="5">
+        <v>2638</v>
+      </c>
+      <c r="C26" s="5">
+        <v>1537</v>
+      </c>
+      <c r="D26" s="5">
+        <v>7963</v>
+      </c>
+      <c r="E26" s="5">
+        <v>1547</v>
+      </c>
+      <c r="F26" s="6">
+        <f t="shared" si="0"/>
+        <v>3.0185746777862</v>
+      </c>
+      <c r="G26" s="7">
+        <f t="shared" si="1"/>
+        <v>0.586429112964367</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B27" s="5">
+        <v>156</v>
+      </c>
+      <c r="C27" s="5">
+        <v>101</v>
+      </c>
+      <c r="D27" s="5">
+        <v>295</v>
+      </c>
+      <c r="E27" s="5">
+        <v>93</v>
+      </c>
+      <c r="F27" s="6">
+        <f t="shared" si="0"/>
+        <v>1.89102564102564</v>
+      </c>
+      <c r="G27" s="7">
+        <f t="shared" si="1"/>
+        <v>0.596153846153846</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B28" s="5">
+        <v>4343</v>
+      </c>
+      <c r="C28" s="5">
+        <v>2486</v>
+      </c>
+      <c r="D28" s="5">
+        <v>10168</v>
+      </c>
+      <c r="E28" s="5">
+        <v>2710</v>
+      </c>
+      <c r="F28" s="6">
+        <f t="shared" si="0"/>
+        <v>2.34123877504029</v>
+      </c>
+      <c r="G28" s="7">
+        <f t="shared" si="1"/>
+        <v>0.623992631821322</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B29" s="5">
+        <v>2926</v>
+      </c>
+      <c r="C29" s="5">
+        <v>1780</v>
+      </c>
+      <c r="D29" s="5">
+        <v>5272</v>
+      </c>
+      <c r="E29" s="5">
+        <v>1766</v>
+      </c>
+      <c r="F29" s="6">
+        <f t="shared" si="0"/>
+        <v>1.80177717019822</v>
+      </c>
+      <c r="G29" s="7">
+        <f t="shared" si="1"/>
+        <v>0.603554340396446</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B30" s="5">
+        <v>636</v>
+      </c>
+      <c r="C30" s="5">
+        <v>362</v>
+      </c>
+      <c r="D30" s="5">
+        <v>2205</v>
+      </c>
+      <c r="E30" s="5">
+        <v>402</v>
+      </c>
+      <c r="F30" s="6">
+        <f t="shared" si="0"/>
+        <v>3.46698113207547</v>
+      </c>
+      <c r="G30" s="7">
+        <f t="shared" si="1"/>
+        <v>0.632075471698113</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B31" s="5">
+        <v>1105</v>
+      </c>
+      <c r="C31" s="5">
+        <v>612</v>
+      </c>
+      <c r="D31" s="5">
+        <v>1789</v>
+      </c>
+      <c r="E31" s="5">
+        <v>735</v>
+      </c>
+      <c r="F31" s="6">
+        <f t="shared" si="0"/>
+        <v>1.61900452488688</v>
+      </c>
+      <c r="G31" s="7">
+        <f t="shared" si="1"/>
+        <v>0.665158371040724</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32" s="5">
+        <v>3339</v>
+      </c>
+      <c r="C32" s="5">
+        <v>1925</v>
+      </c>
+      <c r="D32" s="5">
+        <v>7353</v>
+      </c>
+      <c r="E32" s="5">
+        <v>1883</v>
+      </c>
+      <c r="F32" s="6">
+        <f t="shared" si="0"/>
+        <v>2.20215633423181</v>
+      </c>
+      <c r="G32" s="7">
+        <f t="shared" si="1"/>
+        <v>0.563941299790356</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33" s="5">
+        <v>34</v>
+      </c>
+      <c r="C33" s="5">
+        <v>25</v>
+      </c>
+      <c r="D33" s="5">
+        <v>49</v>
+      </c>
+      <c r="E33" s="5">
+        <v>24</v>
+      </c>
+      <c r="F33" s="6">
+        <f t="shared" si="0"/>
+        <v>1.44117647058824</v>
+      </c>
+      <c r="G33" s="7">
+        <f t="shared" si="1"/>
+        <v>0.705882352941177</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" s="5">
+        <v>11</v>
+      </c>
+      <c r="C34" s="5">
         <v>7</v>
       </c>
-      <c r="B3" s="4">
-        <v>7740</v>
-      </c>
-      <c r="C3" s="5">
-        <v>26718</v>
-      </c>
-      <c r="D3" s="5">
-        <v>5805</v>
-      </c>
-      <c r="E3" s="6">
-        <f t="shared" si="0"/>
-        <v>3.45193798449612</v>
-      </c>
-      <c r="F3" s="7">
-        <f t="shared" ref="F2:F35" si="1">D3/B3</f>
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="4">
-        <v>8437</v>
-      </c>
-      <c r="C4" s="5">
-        <v>14818</v>
-      </c>
-      <c r="D4" s="5">
-        <v>5466</v>
-      </c>
-      <c r="E4" s="6">
-        <f t="shared" si="0"/>
-        <v>1.75631148512504</v>
-      </c>
-      <c r="F4" s="7">
-        <f t="shared" si="1"/>
-        <v>0.647860613962309</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="4">
-        <v>3709</v>
-      </c>
-      <c r="C5" s="5">
-        <v>6562</v>
-      </c>
-      <c r="D5" s="5">
-        <v>2402</v>
-      </c>
-      <c r="E5" s="6">
-        <f t="shared" si="0"/>
-        <v>1.76921002965759</v>
-      </c>
-      <c r="F5" s="7">
-        <f t="shared" si="1"/>
-        <v>0.647613912105689</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="4">
-        <v>2946</v>
-      </c>
-      <c r="C6" s="5">
-        <v>8930</v>
-      </c>
-      <c r="D6" s="5">
-        <v>1803</v>
-      </c>
-      <c r="E6" s="6">
-        <f t="shared" si="0"/>
-        <v>3.03122878479294</v>
-      </c>
-      <c r="F6" s="7">
-        <f t="shared" si="1"/>
-        <v>0.612016293279022</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="4">
-        <v>10854</v>
-      </c>
-      <c r="C7" s="5">
-        <v>49571</v>
-      </c>
-      <c r="D7" s="5">
-        <v>7670</v>
-      </c>
-      <c r="E7" s="6">
-        <f t="shared" si="0"/>
-        <v>4.56707204717155</v>
-      </c>
-      <c r="F7" s="7">
-        <f t="shared" si="1"/>
-        <v>0.706651925557398</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="4">
-        <v>3695</v>
-      </c>
-      <c r="C8" s="5">
-        <v>11077</v>
-      </c>
-      <c r="D8" s="5">
-        <v>2461</v>
-      </c>
-      <c r="E8" s="6">
-        <f t="shared" si="0"/>
-        <v>2.9978349120433</v>
-      </c>
-      <c r="F8" s="7">
-        <f t="shared" si="1"/>
-        <v>0.666035182679296</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="4">
-        <v>6530</v>
-      </c>
-      <c r="C9" s="5">
-        <v>18479</v>
-      </c>
-      <c r="D9" s="5">
-        <v>4508</v>
-      </c>
-      <c r="E9" s="6">
-        <f t="shared" si="0"/>
-        <v>2.82986217457887</v>
-      </c>
-      <c r="F9" s="7">
-        <f t="shared" si="1"/>
-        <v>0.690352220520674</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="4">
-        <v>2843</v>
-      </c>
-      <c r="C10" s="5">
-        <v>17024</v>
-      </c>
-      <c r="D10" s="5">
-        <v>1727</v>
-      </c>
-      <c r="E10" s="6">
-        <f t="shared" si="0"/>
-        <v>5.98804080196975</v>
-      </c>
-      <c r="F10" s="7">
-        <f t="shared" si="1"/>
-        <v>0.607456911712979</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" s="4">
-        <v>22242</v>
-      </c>
-      <c r="C11" s="5">
-        <v>100389</v>
-      </c>
-      <c r="D11" s="5">
-        <v>15164</v>
-      </c>
-      <c r="E11" s="6">
-        <f t="shared" si="0"/>
-        <v>4.51348799568384</v>
-      </c>
-      <c r="F11" s="7">
-        <f t="shared" si="1"/>
-        <v>0.681773221832569</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="4">
-        <v>7876</v>
-      </c>
-      <c r="C12" s="5">
-        <v>25577</v>
-      </c>
-      <c r="D12" s="5">
-        <v>5440</v>
-      </c>
-      <c r="E12" s="6">
-        <f t="shared" si="0"/>
-        <v>3.24746063991874</v>
-      </c>
-      <c r="F12" s="7">
-        <f t="shared" si="1"/>
-        <v>0.69070594210259</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" s="4">
-        <v>12645</v>
-      </c>
-      <c r="C13" s="5">
-        <v>44180</v>
-      </c>
-      <c r="D13" s="5">
-        <v>8746</v>
-      </c>
-      <c r="E13" s="6">
-        <f t="shared" si="0"/>
-        <v>3.49387109529458</v>
-      </c>
-      <c r="F13" s="7">
-        <f t="shared" si="1"/>
-        <v>0.691656781336497</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14" s="4">
-        <v>10297</v>
-      </c>
-      <c r="C14" s="5">
-        <v>25981</v>
-      </c>
-      <c r="D14" s="5">
-        <v>7349</v>
-      </c>
-      <c r="E14" s="6">
-        <f t="shared" si="0"/>
-        <v>2.52316208604448</v>
-      </c>
-      <c r="F14" s="7">
-        <f t="shared" si="1"/>
-        <v>0.713703020297174</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15" s="4">
-        <v>7671</v>
-      </c>
-      <c r="C15" s="5">
-        <v>12346</v>
-      </c>
-      <c r="D15" s="5">
-        <v>5081</v>
-      </c>
-      <c r="E15" s="6">
-        <f t="shared" si="0"/>
-        <v>1.60943814365793</v>
-      </c>
-      <c r="F15" s="7">
-        <f t="shared" si="1"/>
-        <v>0.662364750358493</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16" s="4">
-        <v>32810</v>
-      </c>
-      <c r="C16" s="5">
-        <v>76191</v>
-      </c>
-      <c r="D16" s="5">
-        <v>24750</v>
-      </c>
-      <c r="E16" s="6">
-        <f t="shared" si="0"/>
-        <v>2.32218835720817</v>
-      </c>
-      <c r="F16" s="7">
-        <f t="shared" si="1"/>
-        <v>0.754343188052423</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B17" s="4">
-        <v>10347</v>
-      </c>
-      <c r="C17" s="5">
-        <v>16527</v>
-      </c>
-      <c r="D17" s="5">
-        <v>6794</v>
-      </c>
-      <c r="E17" s="6">
-        <f t="shared" si="0"/>
-        <v>1.59727457233981</v>
-      </c>
-      <c r="F17" s="7">
-        <f t="shared" si="1"/>
-        <v>0.656615444090074</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18" s="4">
-        <v>7978</v>
-      </c>
-      <c r="C18" s="5">
-        <v>24456</v>
-      </c>
-      <c r="D18" s="5">
-        <v>5544</v>
-      </c>
-      <c r="E18" s="6">
-        <f t="shared" si="0"/>
-        <v>3.06542993231386</v>
-      </c>
-      <c r="F18" s="7">
-        <f t="shared" si="1"/>
-        <v>0.694911005264477</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B19" s="4">
-        <v>9037</v>
-      </c>
-      <c r="C19" s="5">
-        <v>27480</v>
-      </c>
-      <c r="D19" s="5">
-        <v>6141</v>
-      </c>
-      <c r="E19" s="6">
-        <f t="shared" si="0"/>
-        <v>3.04083213455793</v>
-      </c>
-      <c r="F19" s="7">
-        <f t="shared" si="1"/>
-        <v>0.67953967024455</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B20" s="4">
-        <v>15700</v>
-      </c>
-      <c r="C20" s="5">
-        <v>63799</v>
-      </c>
-      <c r="D20" s="5">
-        <v>10558</v>
-      </c>
-      <c r="E20" s="6">
-        <f t="shared" si="0"/>
-        <v>4.06363057324841</v>
-      </c>
-      <c r="F20" s="7">
-        <f t="shared" si="1"/>
-        <v>0.672484076433121</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B21" s="4">
-        <v>3127</v>
-      </c>
-      <c r="C21" s="5">
-        <v>6319</v>
-      </c>
-      <c r="D21" s="5">
-        <v>2069</v>
-      </c>
-      <c r="E21" s="6">
-        <f t="shared" si="0"/>
-        <v>2.02078669651423</v>
-      </c>
-      <c r="F21" s="7">
-        <f t="shared" si="1"/>
-        <v>0.661656539814519</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B22" s="4">
-        <v>1510</v>
-      </c>
-      <c r="C22" s="5">
-        <v>5033</v>
-      </c>
-      <c r="D22" s="5">
-        <v>1047</v>
-      </c>
-      <c r="E22" s="6">
-        <f t="shared" si="0"/>
-        <v>3.33311258278146</v>
-      </c>
-      <c r="F22" s="7">
-        <f t="shared" si="1"/>
-        <v>0.693377483443709</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B23" s="4">
-        <v>5003</v>
-      </c>
-      <c r="C23" s="5">
-        <v>20436</v>
-      </c>
-      <c r="D23" s="5">
-        <v>3363</v>
-      </c>
-      <c r="E23" s="6">
-        <f t="shared" si="0"/>
-        <v>4.08474915050969</v>
-      </c>
-      <c r="F23" s="7">
-        <f t="shared" si="1"/>
-        <v>0.672196681990806</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B24" s="4">
-        <v>7095</v>
-      </c>
-      <c r="C24" s="5">
-        <v>17938</v>
-      </c>
-      <c r="D24" s="5">
-        <v>4907</v>
-      </c>
-      <c r="E24" s="6">
-        <f t="shared" si="0"/>
-        <v>2.52825933756166</v>
-      </c>
-      <c r="F24" s="7">
-        <f t="shared" si="1"/>
-        <v>0.691613812544045</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B25" s="4">
-        <v>2320</v>
-      </c>
-      <c r="C25" s="5">
-        <v>5343</v>
-      </c>
-      <c r="D25" s="5">
-        <v>1400</v>
-      </c>
-      <c r="E25" s="6">
-        <f t="shared" si="0"/>
-        <v>2.30301724137931</v>
-      </c>
-      <c r="F25" s="7">
-        <f t="shared" si="1"/>
-        <v>0.603448275862069</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B26" s="4">
-        <v>2638</v>
-      </c>
-      <c r="C26" s="5">
-        <v>7963</v>
-      </c>
-      <c r="D26" s="5">
-        <v>1547</v>
-      </c>
-      <c r="E26" s="6">
-        <f t="shared" si="0"/>
-        <v>3.0185746777862</v>
-      </c>
-      <c r="F26" s="7">
-        <f t="shared" si="1"/>
-        <v>0.586429112964367</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B27" s="4">
-        <v>156</v>
-      </c>
-      <c r="C27" s="5">
-        <v>295</v>
-      </c>
-      <c r="D27" s="5">
-        <v>93</v>
-      </c>
-      <c r="E27" s="6">
-        <f t="shared" si="0"/>
-        <v>1.89102564102564</v>
-      </c>
-      <c r="F27" s="7">
-        <f t="shared" si="1"/>
-        <v>0.596153846153846</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B28" s="4">
-        <v>4343</v>
-      </c>
-      <c r="C28" s="5">
-        <v>10168</v>
-      </c>
-      <c r="D28" s="5">
-        <v>2710</v>
-      </c>
-      <c r="E28" s="6">
-        <f t="shared" si="0"/>
-        <v>2.34123877504029</v>
-      </c>
-      <c r="F28" s="7">
-        <f t="shared" si="1"/>
-        <v>0.623992631821322</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B29" s="4">
-        <v>2926</v>
-      </c>
-      <c r="C29" s="5">
-        <v>5272</v>
-      </c>
-      <c r="D29" s="5">
-        <v>1766</v>
-      </c>
-      <c r="E29" s="6">
-        <f t="shared" si="0"/>
-        <v>1.80177717019822</v>
-      </c>
-      <c r="F29" s="7">
-        <f t="shared" si="1"/>
-        <v>0.603554340396446</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B30" s="4">
-        <v>636</v>
-      </c>
-      <c r="C30" s="5">
-        <v>2205</v>
-      </c>
-      <c r="D30" s="5">
-        <v>402</v>
-      </c>
-      <c r="E30" s="6">
-        <f t="shared" si="0"/>
-        <v>3.46698113207547</v>
-      </c>
-      <c r="F30" s="7">
-        <f t="shared" si="1"/>
-        <v>0.632075471698113</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B31" s="4">
-        <v>1105</v>
-      </c>
-      <c r="C31" s="5">
-        <v>1789</v>
-      </c>
-      <c r="D31" s="5">
-        <v>735</v>
-      </c>
-      <c r="E31" s="6">
-        <f t="shared" si="0"/>
-        <v>1.61900452488688</v>
-      </c>
-      <c r="F31" s="7">
-        <f t="shared" si="1"/>
-        <v>0.665158371040724</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B32" s="4">
-        <v>3339</v>
-      </c>
-      <c r="C32" s="5">
-        <v>7353</v>
-      </c>
-      <c r="D32" s="5">
-        <v>1883</v>
-      </c>
-      <c r="E32" s="6">
-        <f t="shared" si="0"/>
-        <v>2.20215633423181</v>
-      </c>
-      <c r="F32" s="7">
-        <f t="shared" si="1"/>
-        <v>0.563941299790356</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B33" s="4">
-        <v>34</v>
-      </c>
-      <c r="C33" s="5">
-        <v>49</v>
-      </c>
-      <c r="D33" s="5">
-        <v>24</v>
-      </c>
-      <c r="E33" s="6">
-        <f t="shared" si="0"/>
-        <v>1.44117647058824</v>
-      </c>
-      <c r="F33" s="7">
-        <f t="shared" si="1"/>
-        <v>0.705882352941177</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B34" s="4">
-        <v>11</v>
-      </c>
-      <c r="C34" s="5">
+      <c r="D34" s="5">
         <v>0</v>
       </c>
-      <c r="D34" s="5">
+      <c r="E34" s="5">
         <v>6</v>
       </c>
-      <c r="E34" s="6">
+      <c r="F34" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F34" s="7">
+      <c r="G34" s="7">
         <f t="shared" si="1"/>
         <v>0.545454545454545</v>
       </c>
     </row>
-    <row r="35" spans="1:6">
-      <c r="A35" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B35" s="4">
+    <row r="35" spans="1:7">
+      <c r="A35" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35" s="5">
         <v>11</v>
       </c>
       <c r="C35" s="5">
         <v>0</v>
       </c>
       <c r="D35" s="5">
+        <v>0</v>
+      </c>
+      <c r="E35" s="5">
         <v>8</v>
       </c>
-      <c r="E35" s="6">
+      <c r="F35" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F35" s="7">
+      <c r="G35" s="7">
         <f t="shared" si="1"/>
         <v>0.727272727272727</v>
       </c>
